--- a/GAURAV SUPER KINGS/BOM.xlsx
+++ b/GAURAV SUPER KINGS/BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gaure\Documents\GitHub\Bluetooth-and-Mioty-Localization\MAIN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gaure\Documents\GitHub\Bluetooth-and-Mioty-Localization\GAURAV SUPER KINGS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3DCD9C-5DA3-47D4-AAB0-CD1AF2347D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048CD336-91A6-4AAF-9501-5905B5AF7C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="173">
   <si>
     <t>S. No.</t>
   </si>
@@ -522,15 +522,9 @@
     <t>https://www.digikey.de/de/products/detail/stmicroelectronics/IIS2MDCTR/7927708?s=N4IgTCBcDaIJJwMpgLIBEDCAVASiAugL5A</t>
   </si>
   <si>
-    <t xml:space="preserve"> magnetoresistiv Sensor X, Y, Z Achse 12-LGA (2x2)</t>
-  </si>
-  <si>
     <t>220u</t>
   </si>
   <si>
-    <t>C33</t>
-  </si>
-  <si>
     <t>GRM155R61A106ME11D</t>
   </si>
   <si>
@@ -544,6 +538,12 @@
   </si>
   <si>
     <t>GRM155R71C224KA12D</t>
+  </si>
+  <si>
+    <t>RZ1</t>
+  </si>
+  <si>
+    <t>magnetoresistiv Sensor X, Y, Z Achse 12-LGA (2x2)</t>
   </si>
 </sst>
 </file>
@@ -898,16 +898,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" customWidth="1"/>
-    <col min="5" max="5" width="35.140625" customWidth="1"/>
-    <col min="6" max="6" width="138.140625" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" customWidth="1"/>
+    <col min="5" max="5" width="35.109375" customWidth="1"/>
+    <col min="6" max="6" width="138.109375" customWidth="1"/>
+    <col min="7" max="7" width="28.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -930,12 +930,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -955,7 +955,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -975,12 +975,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1020,12 +1020,12 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1045,12 +1045,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>3</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>4</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>5</v>
       </c>
@@ -1150,7 +1150,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>6</v>
       </c>
@@ -1170,12 +1170,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -1215,12 +1215,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>3</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>4</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>5</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>6</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>7</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>8</v>
       </c>
@@ -1377,12 +1377,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>2</v>
       </c>
@@ -1422,7 +1422,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>4</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>5</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>6</v>
       </c>
@@ -1502,12 +1502,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>171</v>
       </c>
       <c r="C36" t="s">
         <v>20</v>
@@ -1522,7 +1522,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>8</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>9</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>10</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>11</v>
       </c>
@@ -1599,13 +1599,13 @@
         <v>49</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>17</v>
       </c>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>2</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>3</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>5</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>6</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>7</v>
       </c>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="F48" s="4"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>8</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>9</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>10</v>
       </c>
@@ -1785,12 +1785,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>80</v>
       </c>
       <c r="D53" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E53" t="s">
         <v>83</v>
@@ -1810,12 +1810,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>2</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>3</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>6</v>
       </c>
@@ -1935,12 +1935,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>159</v>
       </c>
       <c r="D62" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="E62" t="s">
         <v>163</v>
@@ -1960,7 +1960,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>2</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>3</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>4</v>
       </c>
@@ -2014,13 +2014,13 @@
         <v>81</v>
       </c>
       <c r="E65" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F65" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>5</v>
       </c>
@@ -2031,16 +2031,16 @@
         <v>29</v>
       </c>
       <c r="D66" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E66" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F66" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>6</v>
       </c>
@@ -2060,25 +2060,8 @@
         <v>107</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>7</v>
-      </c>
-      <c r="B68" t="s">
-        <v>167</v>
-      </c>
-      <c r="C68" t="s">
-        <v>29</v>
-      </c>
-      <c r="D68" t="s">
-        <v>105</v>
-      </c>
-      <c r="E68" t="s">
-        <v>108</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>107</v>
-      </c>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F68" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2097,27 +2080,26 @@
     <hyperlink ref="F38" r:id="rId13" xr:uid="{3D8C70F3-86D1-408F-B991-32BBA9AE0284}"/>
     <hyperlink ref="F37" r:id="rId14" xr:uid="{B4530D85-708B-4214-B1E4-BAFC599C8674}"/>
     <hyperlink ref="F35" r:id="rId15" xr:uid="{467D3286-50FF-4216-8937-835A6BA4C3A8}"/>
-    <hyperlink ref="F36" r:id="rId16" xr:uid="{283DFAF0-B027-460E-BEA3-E28DB7D75637}"/>
-    <hyperlink ref="F39" r:id="rId17" xr:uid="{217435C8-5FF7-4B86-B4E9-BFA135B39084}"/>
-    <hyperlink ref="F40" r:id="rId18" xr:uid="{F9702DF9-CC1B-42B0-96AD-216A11C735E3}"/>
-    <hyperlink ref="F42" r:id="rId19" xr:uid="{A27D8FF2-1762-470C-89EB-CA17719CDF2A}"/>
-    <hyperlink ref="F43" r:id="rId20" xr:uid="{CB456E9B-1680-41E5-A8F6-0AC98E1B2684}"/>
-    <hyperlink ref="F44" r:id="rId21" xr:uid="{84C8FBE4-112A-49FF-8A0D-F9CB3B1FE98A}"/>
-    <hyperlink ref="F45" r:id="rId22" xr:uid="{7AB50742-9609-4684-BB22-23FCC3D0AFAC}"/>
-    <hyperlink ref="F46" r:id="rId23" xr:uid="{CEB15CA5-20DF-48F1-A71E-97BE776E1A3A}"/>
-    <hyperlink ref="F49" r:id="rId24" display="https://www.digikey.de/de/products/detail/te-connectivity-linx/CONMHF1-SMD-G-T/15293397?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20179951824&amp;gbraid=0AAAAADrbLlgcW0wDpxdB3QLoBqEJ77uUK&amp;gclid=Cj0KCQjw6bfHBhDNARIsAIGsqLjLl1jPmqBYngNawJjpDc2NL71_ijr013dRm_6SUY6Z-PSxDqZcU4AaAjl_EALw_wcB" xr:uid="{72808A11-5911-4A58-ADDF-A972CB0F47C2}"/>
-    <hyperlink ref="F53" r:id="rId25" xr:uid="{EBB4519B-B72F-4CC1-9062-C7A3B3B0DDF2}"/>
-    <hyperlink ref="F23" r:id="rId26" xr:uid="{2444E7F9-12BD-42E6-AE3F-D56336F9D828}"/>
-    <hyperlink ref="F24" r:id="rId27" xr:uid="{DADCDF1D-4918-481F-94A3-52B31B5558B5}"/>
-    <hyperlink ref="F25" r:id="rId28" xr:uid="{9C9C4086-80EB-43C3-B1A9-F24609908460}"/>
-    <hyperlink ref="F26" r:id="rId29" xr:uid="{F2D7E8A1-E468-4CBC-93D7-F41721223FCD}"/>
-    <hyperlink ref="F27" r:id="rId30" xr:uid="{9072A8B7-BB60-469A-8C9A-751137450A1E}"/>
-    <hyperlink ref="F28" r:id="rId31" xr:uid="{3F0B231E-8513-40C3-91FD-3A197A6A2489}"/>
-    <hyperlink ref="F56" r:id="rId32" xr:uid="{48C1C764-1533-418B-92FF-0715C755090E}"/>
-    <hyperlink ref="F57" r:id="rId33" xr:uid="{89295D1F-98D7-49F1-8ECD-A63A31CB2E30}"/>
-    <hyperlink ref="F60" r:id="rId34" xr:uid="{0B762A7B-77E3-4020-95E2-B10D2ABA3A5A}"/>
-    <hyperlink ref="F67" r:id="rId35" xr:uid="{83551B11-2746-4512-AE7F-59155A0DC3CB}"/>
-    <hyperlink ref="F68" r:id="rId36" xr:uid="{76CCA5CE-6CE1-43B1-941A-F96B8273F8E3}"/>
+    <hyperlink ref="F39" r:id="rId16" xr:uid="{217435C8-5FF7-4B86-B4E9-BFA135B39084}"/>
+    <hyperlink ref="F40" r:id="rId17" xr:uid="{F9702DF9-CC1B-42B0-96AD-216A11C735E3}"/>
+    <hyperlink ref="F42" r:id="rId18" xr:uid="{A27D8FF2-1762-470C-89EB-CA17719CDF2A}"/>
+    <hyperlink ref="F43" r:id="rId19" xr:uid="{CB456E9B-1680-41E5-A8F6-0AC98E1B2684}"/>
+    <hyperlink ref="F44" r:id="rId20" xr:uid="{84C8FBE4-112A-49FF-8A0D-F9CB3B1FE98A}"/>
+    <hyperlink ref="F45" r:id="rId21" xr:uid="{7AB50742-9609-4684-BB22-23FCC3D0AFAC}"/>
+    <hyperlink ref="F46" r:id="rId22" xr:uid="{CEB15CA5-20DF-48F1-A71E-97BE776E1A3A}"/>
+    <hyperlink ref="F49" r:id="rId23" display="https://www.digikey.de/de/products/detail/te-connectivity-linx/CONMHF1-SMD-G-T/15293397?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20179951824&amp;gbraid=0AAAAADrbLlgcW0wDpxdB3QLoBqEJ77uUK&amp;gclid=Cj0KCQjw6bfHBhDNARIsAIGsqLjLl1jPmqBYngNawJjpDc2NL71_ijr013dRm_6SUY6Z-PSxDqZcU4AaAjl_EALw_wcB" xr:uid="{72808A11-5911-4A58-ADDF-A972CB0F47C2}"/>
+    <hyperlink ref="F53" r:id="rId24" xr:uid="{EBB4519B-B72F-4CC1-9062-C7A3B3B0DDF2}"/>
+    <hyperlink ref="F23" r:id="rId25" xr:uid="{2444E7F9-12BD-42E6-AE3F-D56336F9D828}"/>
+    <hyperlink ref="F24" r:id="rId26" xr:uid="{DADCDF1D-4918-481F-94A3-52B31B5558B5}"/>
+    <hyperlink ref="F25" r:id="rId27" xr:uid="{9C9C4086-80EB-43C3-B1A9-F24609908460}"/>
+    <hyperlink ref="F26" r:id="rId28" xr:uid="{F2D7E8A1-E468-4CBC-93D7-F41721223FCD}"/>
+    <hyperlink ref="F27" r:id="rId29" xr:uid="{9072A8B7-BB60-469A-8C9A-751137450A1E}"/>
+    <hyperlink ref="F28" r:id="rId30" xr:uid="{3F0B231E-8513-40C3-91FD-3A197A6A2489}"/>
+    <hyperlink ref="F56" r:id="rId31" xr:uid="{48C1C764-1533-418B-92FF-0715C755090E}"/>
+    <hyperlink ref="F57" r:id="rId32" xr:uid="{89295D1F-98D7-49F1-8ECD-A63A31CB2E30}"/>
+    <hyperlink ref="F60" r:id="rId33" xr:uid="{0B762A7B-77E3-4020-95E2-B10D2ABA3A5A}"/>
+    <hyperlink ref="F67" r:id="rId34" xr:uid="{83551B11-2746-4512-AE7F-59155A0DC3CB}"/>
+    <hyperlink ref="F36" r:id="rId35" xr:uid="{283DFAF0-B027-460E-BEA3-E28DB7D75637}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
